--- a/Result/profitability/6122.xlsx
+++ b/Result/profitability/6122.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01125</v>
+        <v>1.00875</v>
       </c>
       <c r="N2" t="n">
-        <v>13.3025</v>
+        <v>13.31625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.66</v>
       </c>
       <c r="M3" t="n">
-        <v>0.94625</v>
+        <v>0.97</v>
       </c>
       <c r="N3" t="n">
-        <v>13.24125</v>
+        <v>13.49</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.59</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8987499999999999</v>
+        <v>0.9025</v>
       </c>
       <c r="N4" t="n">
-        <v>13.39625</v>
+        <v>13.22125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8462499999999999</v>
+        <v>0.85625</v>
       </c>
       <c r="N5" t="n">
-        <v>12.69</v>
+        <v>12.635</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.98</v>
       </c>
       <c r="M6" t="n">
-        <v>0.83375</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>11.9125</v>
+        <v>11.79375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.70125</v>
+        <v>0.68</v>
       </c>
       <c r="N7" t="n">
-        <v>10.81375</v>
+        <v>10.67375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0.61</v>
+        <v>0.62625</v>
       </c>
       <c r="N8" t="n">
-        <v>10.2075</v>
+        <v>10.04</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.63</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>10.07375</v>
@@ -1772,7 +1772,7 @@
         <v>0.64</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6012500000000001</v>
+        <v>0.60125</v>
       </c>
       <c r="N11" t="n">
         <v>10.2925</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6122</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D75" t="n">
+        <v>893</v>
+      </c>
+      <c r="E75" t="n">
+        <v>142</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>107</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>111</v>
+      </c>
+      <c r="K75" t="n">
+        <v>89</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.13875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.08375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1299999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1262135922330097</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08915502328675984</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07999999999999985</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.07407407407407396</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4400000000000013</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03113941967445166</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
